--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -12531,7 +12531,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13389,16 +13389,16 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O72" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.846892856697124</v>
+        <v>0.844954886773332</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15269,16 +15269,16 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O82" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.8585206762398764</v>
+        <v>0.8643345860112523</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16209,16 +16209,16 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="O87" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.506848031093731</v>
+        <v>0.5803042674841269</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -16767,16 +16767,16 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="O90" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0717048871803057</v>
+        <v>0.1375958645892353</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93658</v>
+        <v>93714</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -16757,16 +16757,16 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="O88" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.8643345860112523</v>
+        <v>0.8604586461636684</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17697,16 +17697,16 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="O93" t="n">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.6390692565964434</v>
+        <v>0.7565992348210768</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -18255,16 +18255,16 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O96" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.1860451126840364</v>
+        <v>0.2151146615409171</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93760</v>
+        <v>93805</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>252</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>59</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.6549880448029585</v>
       </c>
@@ -1468,9 +1462,6 @@
       <c r="O6" t="n">
         <v>69</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.227378327896255</v>
       </c>
@@ -1864,9 +1855,6 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -2012,9 +2000,6 @@
       <c r="O9" t="n">
         <v>446</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.8643345860112523</v>
       </c>
@@ -2160,9 +2145,6 @@
       <c r="O10" t="n">
         <v>34</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.6014517807704721</v>
       </c>
@@ -2805,7 +2787,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2952,9 +2934,6 @@
       <c r="O14" t="n">
         <v>50</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.4672440214141673</v>
       </c>
@@ -3348,9 +3327,6 @@
       <c r="O16" t="n">
         <v>263</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3741,9 +3717,6 @@
       <c r="O18" t="n">
         <v>76</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.8437134136444889</v>
       </c>
@@ -4051,9 +4024,6 @@
       <c r="O20" t="n">
         <v>87</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>1.5475639786518</v>
       </c>
@@ -4447,9 +4417,6 @@
       <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -4595,9 +4562,6 @@
       <c r="O23" t="n">
         <v>329</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.6375921049275831</v>
       </c>
@@ -4743,9 +4707,6 @@
       <c r="O24" t="n">
         <v>39</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.6899005720602475</v>
       </c>
@@ -5388,7 +5349,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5535,9 +5496,6 @@
       <c r="O28" t="n">
         <v>46</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.4298644997010339</v>
       </c>
@@ -5931,9 +5889,6 @@
       <c r="O30" t="n">
         <v>260</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6324,9 +6279,6 @@
       <c r="O32" t="n">
         <v>66</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.7326984907965298</v>
       </c>
@@ -6634,9 +6586,6 @@
       <c r="O34" t="n">
         <v>86</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.529775886943158</v>
       </c>
@@ -7030,9 +6979,6 @@
       <c r="O36" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -7178,9 +7124,6 @@
       <c r="O37" t="n">
         <v>417</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.8081334582212831</v>
       </c>
@@ -7326,9 +7269,6 @@
       <c r="O38" t="n">
         <v>43</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.7606596050920676</v>
       </c>
@@ -7971,7 +7911,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8118,9 +8058,6 @@
       <c r="O42" t="n">
         <v>65</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.6074172278384175</v>
       </c>
@@ -8514,9 +8451,6 @@
       <c r="O44" t="n">
         <v>233</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8907,9 +8841,6 @@
       <c r="O46" t="n">
         <v>72</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.7993074445053052</v>
       </c>
@@ -9217,9 +9148,6 @@
       <c r="O48" t="n">
         <v>85</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.511987795234517</v>
       </c>
@@ -9613,9 +9541,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -9761,9 +9686,6 @@
       <c r="O51" t="n">
         <v>564</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>1.093015037018714</v>
       </c>
@@ -9909,9 +9831,6 @@
       <c r="O52" t="n">
         <v>32</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.566072264254562</v>
       </c>
@@ -10305,9 +10224,6 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -10554,7 +10470,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10701,9 +10617,6 @@
       <c r="O56" t="n">
         <v>65</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.6074172278384175</v>
       </c>
@@ -11097,9 +11010,6 @@
       <c r="O58" t="n">
         <v>204</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11652,9 +11562,6 @@
       <c r="O61" t="n">
         <v>59</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>1.049497410809841</v>
       </c>
@@ -12048,9 +11955,6 @@
       <c r="O63" t="n">
         <v>7</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -12196,9 +12100,6 @@
       <c r="O64" t="n">
         <v>391</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.75774624020269</v>
       </c>
@@ -12344,9 +12245,6 @@
       <c r="O65" t="n">
         <v>29</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.5130029894806968</v>
       </c>
@@ -12740,9 +12638,6 @@
       <c r="O67" t="n">
         <v>4</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -12989,7 +12884,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -13136,9 +13031,6 @@
       <c r="O69" t="n">
         <v>42</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.3924849779879006</v>
       </c>
@@ -13532,9 +13424,6 @@
       <c r="O71" t="n">
         <v>471</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>1.729894366993821</v>
       </c>
@@ -14090,9 +13979,6 @@
       <c r="O74" t="n">
         <v>68</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>1.209590236187614</v>
       </c>
@@ -14486,9 +14372,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -14634,9 +14517,6 @@
       <c r="O77" t="n">
         <v>436</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.844954886773332</v>
       </c>
@@ -14782,9 +14662,6 @@
       <c r="O78" t="n">
         <v>23</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.4068644399329664</v>
       </c>
@@ -15178,9 +15055,6 @@
       <c r="O80" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1891260466471829</v>
       </c>
@@ -15427,7 +15301,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15574,9 +15448,6 @@
       <c r="O82" t="n">
         <v>49</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.457899140985884</v>
       </c>
@@ -15970,9 +15841,6 @@
       <c r="O84" t="n">
         <v>7</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.02570968273663853</v>
       </c>
@@ -16361,16 +16229,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O86" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R86" t="n">
-        <v>1.316318786439462</v>
+        <v>1.351894969856744</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -16523,10 +16388,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O87" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -16757,16 +16622,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O88" t="n">
-        <v>444</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="R88" t="n">
-        <v>0.8604586461636684</v>
+        <v>0.8643345860112523</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -16910,9 +16772,6 @@
       <c r="O89" t="n">
         <v>21</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.3714849234170563</v>
       </c>
@@ -17306,9 +17165,6 @@
       <c r="O91" t="n">
         <v>38</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.3551054562747671</v>
       </c>
@@ -17702,9 +17558,6 @@
       <c r="O93" t="n">
         <v>206</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.7565992348210768</v>
       </c>
@@ -17859,16 +17712,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O94" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R94" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18021,10 +17871,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18255,16 +18105,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="O96" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="R96" t="n">
-        <v>0.2151146615409171</v>
+        <v>0.2868195487212228</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18403,16 +18250,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18565,10 +18409,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -18910,7 +18754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93805</v>
+        <v>93851</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -17712,13 +17712,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17871,10 +17871,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93851</v>
+        <v>93853</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -18105,13 +18105,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O96" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R96" t="n">
-        <v>0.2868195487212228</v>
+        <v>0.294571428416391</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93853</v>
+        <v>93857</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -17553,13 +17553,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="O93" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="R93" t="n">
-        <v>0.7565992348210768</v>
+        <v>0.7749632939186758</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17712,13 +17712,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R94" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17871,10 +17871,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93857</v>
+        <v>93865</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O30" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O31" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -8446,10 +8446,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="O44" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8602,10 +8602,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="O45" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O58" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11161,10 +11161,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O59" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -13773,12 +13773,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -13812,25 +13812,19 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>14816</v>
+        <v>224</v>
       </c>
       <c r="O73" t="n">
-        <v>14816</v>
-      </c>
-      <c r="Q73" t="n">
         <v>224</v>
       </c>
-      <c r="R73" t="n">
-        <v>1.048612942612045</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -13840,7 +13834,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
@@ -13850,12 +13844,12 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -13863,47 +13857,47 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13930,17 +13924,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13974,22 +13968,39 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="O74" t="n">
-        <v>68</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.209590236187614</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>224</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -13997,6 +14008,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary hepatitis C notifications without an acute/chronic source split; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14009,12 +14078,12 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CA_ON_PHO_IDTO_HEPATITIS_C_UNSPECIFIED_COURSE_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -14022,47 +14091,47 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14089,17 +14158,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14133,39 +14202,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>68</v>
+        <v>14816</v>
       </c>
       <c r="O75" t="n">
-        <v>68</v>
+        <v>14816</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>224</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.048612942612045</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -14173,67 +14228,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
@@ -14243,12 +14240,12 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -14256,47 +14253,47 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -14328,12 +14325,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14367,81 +14364,95 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="O76" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="R76" t="n">
-        <v>0.06776351400983546</v>
+        <v>1.209590236187614</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14468,17 +14479,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -14512,81 +14523,170 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>436</v>
+        <v>68</v>
       </c>
       <c r="O77" t="n">
-        <v>436</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0.844954886773332</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14618,12 +14718,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14657,95 +14757,81 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O78" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>0.4068644399329664</v>
+        <v>0.06776351400983546</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14772,17 +14858,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14816,170 +14902,81 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>23</v>
+        <v>436</v>
       </c>
       <c r="O79" t="n">
-        <v>23</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>1</v>
+        <v>436</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.844954886773332</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15011,12 +15008,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15050,13 +15047,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O80" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.4068644399329664</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15065,7 +15062,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -15090,7 +15087,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -15103,42 +15100,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15167,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -15209,29 +15206,29 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O81" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -15241,7 +15238,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -15256,7 +15253,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -15291,17 +15288,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15324,7 +15321,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -15337,42 +15334,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15404,12 +15401,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15443,13 +15440,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="O82" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="R82" t="n">
-        <v>0.457899140985884</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -15458,7 +15455,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -15483,7 +15480,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -15496,42 +15493,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15563,12 +15560,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -15602,29 +15599,29 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="O83" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -15634,7 +15631,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -15649,7 +15646,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -15684,17 +15681,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -15717,7 +15714,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -15730,42 +15727,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15797,12 +15794,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15827,22 +15824,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="O84" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="R84" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.457899140985884</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -15851,7 +15848,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -15861,7 +15858,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
@@ -15871,12 +15868,12 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -15884,47 +15881,47 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15956,12 +15953,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15986,38 +15983,38 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="O85" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Hepatitis C (unspecified)</t>
+          <t>Hepatit C</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -16027,7 +16024,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -16042,7 +16039,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -16057,7 +16054,7 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
@@ -16077,17 +16074,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16095,7 +16092,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
@@ -16105,12 +16102,12 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -16118,47 +16115,47 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16190,12 +16187,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16229,13 +16226,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="R86" t="n">
-        <v>1.351894969856744</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -16244,7 +16241,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -16254,7 +16251,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
@@ -16264,12 +16261,12 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -16277,47 +16274,47 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16349,12 +16346,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -16388,29 +16385,29 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="O87" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis C (unspecified)</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -16420,7 +16417,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -16435,7 +16432,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -16450,7 +16447,7 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
@@ -16470,17 +16467,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>Unspecified acquisition status; not combinable with newly acquired without an explicit rule.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16488,7 +16485,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
@@ -16498,12 +16495,12 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -16511,47 +16508,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16583,12 +16580,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16622,81 +16619,95 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="O88" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="R88" t="n">
-        <v>0.8643345860112523</v>
+        <v>1.351894969856744</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16723,17 +16734,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16767,22 +16778,39 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="O89" t="n">
-        <v>21</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.3714849234170563</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>76</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -16790,6 +16818,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -16802,12 +16888,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -16815,47 +16901,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16882,17 +16968,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16926,170 +17012,81 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="O90" t="n">
-        <v>21</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+        <v>446</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.8643345860112523</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17118,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17160,13 +17157,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="O91" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="R91" t="n">
-        <v>0.3551054562747671</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -17175,7 +17172,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -17200,7 +17197,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -17213,42 +17210,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17280,12 +17277,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17319,29 +17316,29 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="O92" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -17366,7 +17363,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -17401,17 +17398,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -17434,7 +17431,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -17447,42 +17444,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17511,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17544,22 +17541,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>211</v>
+        <v>38</v>
       </c>
       <c r="O93" t="n">
-        <v>211</v>
+        <v>38</v>
       </c>
       <c r="R93" t="n">
-        <v>0.7749632939186758</v>
+        <v>0.3551054562747671</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17568,7 +17565,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -17578,7 +17575,7 @@
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
@@ -17588,12 +17585,12 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -17601,47 +17598,47 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17668,17 +17665,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17703,31 +17700,48 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="O94" t="n">
-        <v>16</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.284609467338262</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>38</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -17735,6 +17749,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17747,12 +17819,12 @@
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -17760,47 +17832,47 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17827,17 +17899,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17871,39 +17943,22 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="O95" t="n">
-        <v>16</v>
+        <v>237</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.8704564012261903</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -17911,67 +17966,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
@@ -17981,12 +17978,12 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -17994,47 +17991,47 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18066,12 +18063,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -18105,81 +18102,95 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="O96" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="R96" t="n">
-        <v>0.294571428416391</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18206,17 +18217,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18250,22 +18261,39 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O97" t="n">
-        <v>2</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -18273,6 +18301,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18285,12 +18371,12 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -18298,47 +18384,47 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18365,212 +18451,516 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>152</v>
+      </c>
+      <c r="O98" t="n">
+        <v>152</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.294571428416391</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" t="n">
+        <v>2</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N98" t="n">
+      <c r="N100" t="n">
         <v>2</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O100" t="n">
         <v>2</v>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="W100" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
+      <c r="AC100" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD98" t="inlineStr">
+      <c r="AD100" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE98" t="inlineStr">
+      <c r="AE100" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF98" t="inlineStr">
+      <c r="AF100" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG98" t="inlineStr">
+      <c r="AG100" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH98" t="inlineStr">
+      <c r="AH100" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI98" t="inlineStr">
+      <c r="AI100" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AJ100" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK98" t="inlineStr">
+      <c r="AK100" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AM100" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN98" t="b">
+      <c r="AN100" t="b">
         <v>1</v>
       </c>
-      <c r="AO98" t="inlineStr">
+      <c r="AO100" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP98" t="inlineStr">
+      <c r="AP100" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ98" t="inlineStr">
+      <c r="AQ100" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS98" t="inlineStr">
+      <c r="AS100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT98" t="n">
+      <c r="AT100" t="n">
         <v>1</v>
       </c>
-      <c r="AU98" t="inlineStr">
+      <c r="AU100" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV98" t="inlineStr">
+      <c r="AV100" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW98" t="inlineStr">
+      <c r="AW100" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
+      <c r="AX100" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY98" t="inlineStr">
+      <c r="AY100" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA98" t="inlineStr">
+      <c r="BA100" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB98" t="inlineStr">
+      <c r="BB100" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC98" t="inlineStr">
+      <c r="BC100" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -18692,7 +19082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -18702,7 +19092,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -18722,7 +19112,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -18754,7 +19144,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93865</v>
+        <v>94128</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -17943,13 +17943,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O95" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="R95" t="n">
-        <v>0.8704564012261903</v>
+        <v>0.8814748366847496</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O96" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R96" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -18261,10 +18261,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O97" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -18495,13 +18495,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="O98" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="R98" t="n">
-        <v>0.294571428416391</v>
+        <v>0.3720902253680728</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94128</v>
+        <v>94173</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -16580,12 +16580,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16619,13 +16619,16 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>76</v>
+        <v>15974</v>
       </c>
       <c r="O88" t="n">
-        <v>76</v>
+        <v>15974</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>249</v>
       </c>
       <c r="R88" t="n">
-        <v>1.351894969856744</v>
+        <v>1.130571216609395</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -16634,7 +16637,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -16644,7 +16647,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
@@ -16654,12 +16657,12 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -16667,47 +16670,47 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -16739,12 +16742,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16778,29 +16781,29 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>76</v>
+        <v>15974</v>
       </c>
       <c r="O89" t="n">
-        <v>76</v>
+        <v>15974</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -16810,7 +16813,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -16825,7 +16828,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -16840,7 +16843,7 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
@@ -16860,17 +16863,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+          <t>China CDC hepatitis C series without a source-reported acute/chronic course split.</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16878,7 +16881,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
@@ -16888,12 +16891,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_CN_HEPATITIS_C_UNSPECIFIED_COURSE</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -16901,47 +16904,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -16973,12 +16976,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -17012,81 +17015,95 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="O90" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="R90" t="n">
-        <v>0.8643345860112523</v>
+        <v>1.351894969856744</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17113,17 +17130,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17157,22 +17174,39 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="O91" t="n">
-        <v>21</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.3714849234170563</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>76</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -17180,6 +17214,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17192,12 +17284,12 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -17205,47 +17297,47 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17272,17 +17364,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17316,170 +17408,81 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="O92" t="n">
-        <v>21</v>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN92" t="b">
-        <v>1</v>
+        <v>446</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.8643345860112523</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17511,12 +17514,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17550,13 +17553,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="O93" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="R93" t="n">
-        <v>0.3551054562747671</v>
+        <v>0.3714849234170563</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17565,7 +17568,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -17590,7 +17593,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -17603,42 +17606,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17670,12 +17673,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17709,29 +17712,29 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="O94" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitt C</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -17756,7 +17759,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -17791,17 +17794,17 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -17824,7 +17827,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -17837,42 +17840,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17904,12 +17907,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17934,22 +17937,22 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="O95" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="R95" t="n">
-        <v>0.8814748366847496</v>
+        <v>0.3551054562747671</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17958,7 +17961,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -17968,7 +17971,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
@@ -17978,12 +17981,12 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -17991,47 +17994,47 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18058,17 +18061,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -18093,31 +18096,48 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="O96" t="n">
-        <v>18</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.3201856507555447</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>38</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -18125,6 +18145,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18137,12 +18215,12 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -18150,47 +18228,47 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18217,17 +18295,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18261,39 +18339,22 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="O97" t="n">
-        <v>18</v>
+        <v>240</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.8814748366847496</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -18301,67 +18362,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
@@ -18371,12 +18374,12 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -18384,47 +18387,47 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18456,12 +18459,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -18495,81 +18498,95 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="O98" t="n">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="R98" t="n">
-        <v>0.3720902253680728</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18596,17 +18613,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18640,22 +18657,39 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -18663,6 +18697,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18675,12 +18767,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -18688,47 +18780,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18755,212 +18847,516 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>192</v>
+      </c>
+      <c r="O100" t="n">
+        <v>192</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.3720902253680728</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>2</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="V102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="W102" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
+      <c r="AC102" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD100" t="inlineStr">
+      <c r="AD102" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE100" t="inlineStr">
+      <c r="AE102" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF100" t="inlineStr">
+      <c r="AF102" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG100" t="inlineStr">
+      <c r="AG102" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH100" t="inlineStr">
+      <c r="AH102" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
+      <c r="AI102" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK100" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN100" t="b">
+      <c r="AN102" t="b">
         <v>1</v>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP100" t="inlineStr">
+      <c r="AP102" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ100" t="inlineStr">
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT100" t="n">
+      <c r="AT102" t="n">
         <v>1</v>
       </c>
-      <c r="AU100" t="inlineStr">
+      <c r="AU102" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV100" t="inlineStr">
+      <c r="AV102" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW100" t="inlineStr">
+      <c r="AW102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
+      <c r="AY102" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA100" t="inlineStr">
+      <c r="BA102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB100" t="inlineStr">
+      <c r="BB102" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC100" t="inlineStr">
+      <c r="BC102" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -19082,7 +19478,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -19092,7 +19488,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -19112,7 +19508,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -19122,7 +19518,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -19144,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94173</v>
+        <v>110147</v>
       </c>
     </row>
     <row r="16">
@@ -19154,7 +19550,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>713</v>
+        <v>962</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -15047,13 +15047,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R80" t="n">
-        <v>0.4068644399329664</v>
+        <v>0.4245541981909216</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -17946,13 +17946,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R95" t="n">
-        <v>0.3551054562747671</v>
+        <v>0.3644503367030505</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18105,10 +18105,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O96" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="O97" t="n">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="R97" t="n">
-        <v>0.8814748366847496</v>
+        <v>1.083479486758338</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O98" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R98" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O99" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19036,13 +19036,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O101" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R101" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -19195,10 +19195,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110147</v>
+        <v>110217</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="O97" t="n">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="R97" t="n">
-        <v>1.083479486758338</v>
+        <v>1.208355088622011</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R98" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O99" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110217</v>
+        <v>110254</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -17015,13 +17015,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O90" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R90" t="n">
-        <v>1.351894969856744</v>
+        <v>1.369683061565386</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -17174,10 +17174,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O91" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="O97" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="R97" t="n">
-        <v>1.208355088622011</v>
+        <v>1.182645405885372</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O98" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="R98" t="n">
-        <v>0.426914201007393</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -18657,10 +18657,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O99" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110254</v>
+        <v>110253</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O97" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R97" t="n">
-        <v>1.182645405885372</v>
+        <v>1.186318217704892</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110253</v>
+        <v>110254</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="O97" t="n">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="R97" t="n">
-        <v>1.186318217704892</v>
+        <v>1.131226040412095</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110254</v>
+        <v>110239</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -14902,13 +14902,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="O79" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="R79" t="n">
-        <v>0.844954886773332</v>
+        <v>0.841078946925748</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -15440,13 +15440,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.05673781399415487</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -15599,10 +15599,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O92" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8643345860112523</v>
+        <v>0.8662725559350446</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -17907,12 +17907,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17946,13 +17946,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="O95" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="R95" t="n">
-        <v>0.3644503367030505</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -17999,42 +17999,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18066,12 +18066,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -18105,29 +18105,29 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Hepatit C</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -18187,17 +18187,17 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -18233,42 +18233,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18300,12 +18300,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18330,22 +18330,22 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>308</v>
+        <v>39</v>
       </c>
       <c r="O97" t="n">
-        <v>308</v>
+        <v>39</v>
       </c>
       <c r="R97" t="n">
-        <v>1.131226040412095</v>
+        <v>0.3644503367030505</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
@@ -18374,12 +18374,12 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -18387,47 +18387,47 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18454,17 +18454,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -18489,31 +18489,48 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O98" t="n">
-        <v>29</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0.5158546595505998</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>39</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -18521,6 +18538,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18533,12 +18608,12 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -18546,47 +18621,47 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18613,17 +18688,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18657,39 +18732,22 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>29</v>
+        <v>375</v>
       </c>
       <c r="O99" t="n">
-        <v>29</v>
+        <v>375</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1.377304432319921</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -18697,67 +18755,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
@@ -18767,12 +18767,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -18780,47 +18780,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18852,12 +18852,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18891,81 +18891,95 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="O100" t="n">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="R100" t="n">
-        <v>0.3720902253680728</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18992,17 +19006,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -19036,22 +19050,39 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="O101" t="n">
-        <v>12</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.2122770990954608</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>36</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -19059,6 +19090,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -19071,12 +19160,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
+          <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -19084,47 +19173,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19151,212 +19240,516 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>308</v>
+      </c>
+      <c r="O102" t="n">
+        <v>308</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.5968947365279502</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>19</v>
+      </c>
+      <c r="O103" t="n">
+        <v>19</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.3361054069011462</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>D009</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>丙型肝炎</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N102" t="n">
-        <v>12</v>
-      </c>
-      <c r="O102" t="n">
-        <v>12</v>
-      </c>
-      <c r="U102" t="inlineStr">
+      <c r="N104" t="n">
+        <v>19</v>
+      </c>
+      <c r="O104" t="n">
+        <v>19</v>
+      </c>
+      <c r="U104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
+      <c r="V104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="W102" t="inlineStr">
+      <c r="W104" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>Hepatitt C</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA102" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
+      <c r="AB104" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
+      <c r="AC104" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD102" t="inlineStr">
+      <c r="AD104" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE102" t="inlineStr">
+      <c r="AE104" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF102" t="inlineStr">
+      <c r="AF104" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr">
+      <c r="AG104" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH102" t="inlineStr">
+      <c r="AH104" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI102" t="inlineStr">
+      <c r="AI104" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ102" t="inlineStr">
+      <c r="AJ104" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK102" t="inlineStr">
+      <c r="AK104" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
+      <c r="AM104" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN102" t="b">
+      <c r="AN104" t="b">
         <v>1</v>
       </c>
-      <c r="AO102" t="inlineStr">
+      <c r="AO104" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP102" t="inlineStr">
+      <c r="AP104" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ102" t="inlineStr">
+      <c r="AQ104" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS102" t="inlineStr">
+      <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="AT102" t="n">
+      <c r="AT104" t="n">
         <v>1</v>
       </c>
-      <c r="AU102" t="inlineStr">
+      <c r="AU104" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV102" t="inlineStr">
+      <c r="AV104" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW102" t="inlineStr">
+      <c r="AW104" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
+      <c r="AX104" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr">
+      <c r="AY104" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA102" t="inlineStr">
+      <c r="BA104" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB102" t="inlineStr">
+      <c r="BB104" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC102" t="inlineStr">
+      <c r="BC104" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -19478,7 +19871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -19488,7 +19881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -19508,7 +19901,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -19540,7 +19933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110239</v>
+        <v>110435</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -14902,13 +14902,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O79" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="R79" t="n">
-        <v>0.841078946925748</v>
+        <v>0.844954886773332</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -18732,13 +18732,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="O99" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="R99" t="n">
-        <v>1.377304432319921</v>
+        <v>1.39934130323704</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -19284,13 +19284,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O102" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="R102" t="n">
-        <v>0.5968947365279502</v>
+        <v>0.6104605259944944</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110435</v>
+        <v>110450</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O100" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R100" t="n">
-        <v>0.6403713015110895</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19050,10 +19050,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O101" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110450</v>
+        <v>110455</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -13660,7 +13660,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -17369,12 +17369,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>447</v>
+        <v>2</v>
       </c>
       <c r="O92" t="n">
-        <v>447</v>
+        <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8662725559350446</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -17447,42 +17447,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17553,95 +17553,81 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="O93" t="n">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="R93" t="n">
-        <v>0.3714849234170563</v>
+        <v>0.8662725559350446</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17654,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17717,98 +17703,23 @@
       <c r="O94" t="n">
         <v>21</v>
       </c>
+      <c r="R94" t="n">
+        <v>0.3714849234170563</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN94" t="b">
-        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -17902,17 +17813,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17946,22 +17857,39 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="O95" t="n">
-        <v>7</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.132388232653028</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>21</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -17969,6 +17897,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17986,7 +17972,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+          <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -17999,42 +17985,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18047,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18110,98 +18096,23 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
+      <c r="R96" t="n">
+        <v>0.132388232653028</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -18295,17 +18206,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18339,22 +18250,39 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>39</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0.3644503367030505</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -18362,6 +18290,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis C notifications without a source-reported clinical-course split.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18379,7 +18365,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+          <t>SER_NZ_HEPATITIS_C_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -18392,42 +18378,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18440,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18503,98 +18489,23 @@
       <c r="O98" t="n">
         <v>39</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.3644503367030505</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Hepatit C</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -18688,17 +18599,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18723,31 +18634,48 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>381</v>
+        <v>39</v>
       </c>
       <c r="O99" t="n">
-        <v>381</v>
-      </c>
-      <c r="R99" t="n">
-        <v>1.39934130323704</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>39</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Hepatit C</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -18755,9 +18683,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source does not qualify acute or chronic course.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
@@ -18767,12 +18753,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -18780,47 +18766,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18852,12 +18838,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18891,13 +18877,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="O100" t="n">
-        <v>41</v>
+        <v>423</v>
       </c>
       <c r="R100" t="n">
-        <v>0.7293117600542963</v>
+        <v>1.553599399656871</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -18906,7 +18892,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -18916,7 +18902,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
@@ -18926,12 +18912,12 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_703</t>
+          <t>SER_AU_HEPATITIS_C_UNSPECIFIED</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -18939,47 +18925,47 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19006,7 +18992,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19055,98 +19041,23 @@
       <c r="O101" t="n">
         <v>41</v>
       </c>
+      <c r="R101" t="n">
+        <v>0.7293117600542963</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_703</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_703</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Hepatitis C</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN101" t="b">
-        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -19240,17 +19151,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -19284,81 +19195,170 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="O102" t="n">
-        <v>315</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.6104605259944944</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Source does not qualify acute/chronic course.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_703</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19390,12 +19390,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -19429,95 +19429,81 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>19</v>
+        <v>368</v>
       </c>
       <c r="O103" t="n">
-        <v>19</v>
+        <v>368</v>
       </c>
       <c r="R103" t="n">
-        <v>0.3361054069011462</v>
+        <v>0.7131729319554728</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19530,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -19593,98 +19579,23 @@
       <c r="O104" t="n">
         <v>19</v>
       </c>
+      <c r="R104" t="n">
+        <v>0.3361054069011462</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_203_MONTHLY</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_203_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Hepatitt C</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -19750,6 +19661,240 @@
         </is>
       </c>
       <c r="BC104" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>19</v>
+      </c>
+      <c r="O105" t="n">
+        <v>19</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Hepatitt C</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS clinical course not specified.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_203_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -19871,7 +20016,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -19881,7 +20026,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -19933,7 +20078,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110455</v>
+        <v>110552</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -43793,13 +43793,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O232" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R232" t="n">
-        <v>1.564617835115431</v>
+        <v>1.557272211476391</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -44804,13 +44804,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O239" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R239" t="n">
-        <v>0.9605569522666343</v>
+        <v>0.996133135683917</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -44968,10 +44968,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O240" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -45755,13 +45755,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="O244" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="R244" t="n">
-        <v>0.2534240155468655</v>
+        <v>0.3268802519372613</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -45914,13 +45914,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R245" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -46078,10 +46078,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46317,13 +46317,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O247" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R247" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154348</v>
+        <v>154370</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d009/2026-2029.xlsx
+++ b/diseases/d009/2026-2029.xlsx
@@ -45207,13 +45207,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O241" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R241" t="n">
-        <v>0.844954886773332</v>
+        <v>0.8430169168495401</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154370</v>
+        <v>154369</v>
       </c>
     </row>
     <row r="16">
